--- a/examples/HO_SO_CONG_HOP_TUYEN_A5/HO_SO_THUC_CHIEN_HUB_AND_SPOKE_CONG_A5/GOI_D_QS_DU_TOAN_THANH_TOAN/03_QS_Dien_Giai_Chi_Tiet_Takeoff_Cong_A5.xlsx
+++ b/examples/HO_SO_CONG_HOP_TUYEN_A5/HO_SO_THUC_CHIEN_HUB_AND_SPOKE_CONG_A5/GOI_D_QS_DU_TOAN_THANH_TOAN/03_QS_Dien_Giai_Chi_Tiet_Takeoff_Cong_A5.xlsx
@@ -16,8 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,15 @@
       <name val="Times New Roman"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,8 +65,18 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -78,17 +98,45 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,8 +502,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -515,6 +575,56 @@
           <t>GHI CHÚ</t>
         </is>
       </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>RỘNG LÒNG b (m)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>CAO LÒNG h (m)</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>SỐ KHOANG n</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>CẠNH VÚT c (m)</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>VK TRONG (m2/m)</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>VK HÔNG NGOÀI (m2/m)</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>VK ĐẦU ĐỐT (m2/m)</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>VK TÍNH LẠI (m2/m)</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>CHÊNH LỆCH SO VỚI SỐ ĐANG DÙNG (cột F)</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -663,13 +773,25 @@
         <v>1</v>
       </c>
       <c r="I8" s="3">
-        <f>D8*E8*(F8*G8-2.0*2.0+4*0.5*0.2*0.2)</f>
+        <f>D8*E8*(F8*G8-M8*K8*L8+M8*4*0.5*N8^2)</f>
         <v/>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>2.330 m3/m</t>
         </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -702,13 +824,25 @@
         <v>1</v>
       </c>
       <c r="I9" s="3">
-        <f>D9*E9*(F9*G9-3.0*3.0+4*0.5*0.25*0.25)</f>
+        <f>D9*E9*(F9*G9-M9*K9*L9+M9*4*0.5*N9^2)</f>
         <v/>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>4.085 m3/m</t>
         </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="10">
@@ -741,13 +875,25 @@
         <v>1</v>
       </c>
       <c r="I10" s="3">
-        <f>D10*E10*(F10*G10-2*3.0*3.0+8*0.5*0.25*0.25)</f>
+        <f>D10*E10*(F10*G10-M10*K10*L10+M10*4*0.5*N10^2)</f>
         <v/>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>7.090 m3/m</t>
         </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="11">
@@ -785,8 +931,32 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Trong + ngoài + đầu đốt</t>
-        </is>
+          <t>Cột F = VK m2/m ĐANG DÙNG (không phải bề rộng); P..U là tính lại theo hình học</t>
+        </is>
+      </c>
+      <c r="P11" s="7">
+        <f>$C$17*M8*(2*(K8+L8)-4*N8*(2-SQRT(2)))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="7">
+        <f>$C$18*2*G8+$C$19*F8+$C$20*F8</f>
+        <v/>
+      </c>
+      <c r="R11" s="7">
+        <f>$C$21*2*(F8*G8-M8*K8*L8+M8*4*0.5*N8^2)/E8</f>
+        <v/>
+      </c>
+      <c r="S11" s="7">
+        <f>P11+Q11+R11</f>
+        <v/>
+      </c>
+      <c r="T11" s="8">
+        <f>S11/F11-1</f>
+        <v/>
+      </c>
+      <c r="U11" s="7">
+        <f>IF(ABS(T11)&gt;0.05,"LỆCH &gt;5% - QS xác nhận","Khớp (&lt;=5%)")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -824,8 +994,32 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Trong + ngoài + đầu đốt</t>
-        </is>
+          <t>Cột F = VK m2/m ĐANG DÙNG (không phải bề rộng); P..U là tính lại theo hình học</t>
+        </is>
+      </c>
+      <c r="P12" s="7">
+        <f>$C$17*M9*(2*(K9+L9)-4*N9*(2-SQRT(2)))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="7">
+        <f>$C$18*2*G9+$C$19*F9+$C$20*F9</f>
+        <v/>
+      </c>
+      <c r="R12" s="7">
+        <f>$C$21*2*(F9*G9-M9*K9*L9+M9*4*0.5*N9^2)/E9</f>
+        <v/>
+      </c>
+      <c r="S12" s="7">
+        <f>P12+Q12+R12</f>
+        <v/>
+      </c>
+      <c r="T12" s="8">
+        <f>S12/F12-1</f>
+        <v/>
+      </c>
+      <c r="U12" s="7">
+        <f>IF(ABS(T12)&gt;0.05,"LỆCH &gt;5% - QS xác nhận","Khớp (&lt;=5%)")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -863,11 +1057,102 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Trong + ngoài + đầu đốt</t>
+          <t>Cột F = VK m2/m ĐANG DÙNG (không phải bề rộng); P..U là tính lại theo hình học</t>
+        </is>
+      </c>
+      <c r="P13" s="7">
+        <f>$C$17*M10*(2*(K10+L10)-4*N10*(2-SQRT(2)))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="7">
+        <f>$C$18*2*G10+$C$19*F10+$C$20*F10</f>
+        <v/>
+      </c>
+      <c r="R13" s="7">
+        <f>$C$21*2*(F10*G10-M10*K10*L10+M10*4*0.5*N10^2)/E10</f>
+        <v/>
+      </c>
+      <c r="S13" s="7">
+        <f>P13+Q13+R13</f>
+        <v/>
+      </c>
+      <c r="T13" s="8">
+        <f>S13/F13-1</f>
+        <v/>
+      </c>
+      <c r="U13" s="7">
+        <f>IF(ABS(T13)&gt;0.05,"LỆCH &gt;5% - QS xác nhận","Khớp (&lt;=5%)")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>QUY ƯỚC VÁN KHUÔN (1 = có ván khuôn, 0 = không) - đổi ô vàng, cột P..U của dòng 11-13 tự tính lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ván khuôn mặt trong (lòng cống)</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ván khuôn mặt hông ngoài (2 bên)</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ván khuôn mặt trên (bản nắp)</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ván khuôn mặt đáy (bản đáy)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ván khuôn đầu đốt (2 đầu mỗi đốt)</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="62" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Quy ước: ván khuôn tính theo diện tích bề mặt bê tông tiếp xúc ván khuôn; mặt nào có ván khuôn do biện pháp thi công quyết định (công tắc 1/0 bên dưới). Nguyên tắc đo bóc theo Thông tư 17/2019/TT-BXD (cần đối chiếu điều khoản cụ thể); Thông tư 12/2021/TT-BXD là định mức, không phải đo bóc.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A23:J23"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/examples/HO_SO_CONG_HOP_TUYEN_A5/HO_SO_THUC_CHIEN_HUB_AND_SPOKE_CONG_A5/GOI_D_QS_DU_TOAN_THANH_TOAN/03_QS_Dien_Giai_Chi_Tiet_Takeoff_Cong_A5.xlsx
+++ b/examples/HO_SO_CONG_HOP_TUYEN_A5/HO_SO_THUC_CHIEN_HUB_AND_SPOKE_CONG_A5/GOI_D_QS_DU_TOAN_THANH_TOAN/03_QS_Dien_Giai_Chi_Tiet_Takeoff_Cong_A5.xlsx
@@ -1145,7 +1145,7 @@
     <row r="23" ht="62" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Quy ước: ván khuôn tính theo diện tích bề mặt bê tông tiếp xúc ván khuôn; mặt nào có ván khuôn do biện pháp thi công quyết định (công tắc 1/0 bên dưới). Nguyên tắc đo bóc theo Thông tư 17/2019/TT-BXD (cần đối chiếu điều khoản cụ thể); Thông tư 12/2021/TT-BXD là định mức, không phải đo bóc.</t>
+          <t>Quy ước: ván khuôn tính theo diện tích bề mặt bê tông tiếp xúc ván khuôn; mặt nào có ván khuôn do biện pháp thi công quyết định (công tắc 1/0 bên dưới). Căn cứ đo bóc: Thông tư 13/2021/TT-BXD (cần đối chiếu điều khoản cụ thể và bản sửa đổi hiện hành); Thông tư 12/2021/TT-BXD là định mức, không phải đo bóc.</t>
         </is>
       </c>
     </row>

--- a/examples/HO_SO_CONG_HOP_TUYEN_A5/HO_SO_THUC_CHIEN_HUB_AND_SPOKE_CONG_A5/GOI_D_QS_DU_TOAN_THANH_TOAN/03_QS_Dien_Giai_Chi_Tiet_Takeoff_Cong_A5.xlsx
+++ b/examples/HO_SO_CONG_HOP_TUYEN_A5/HO_SO_THUC_CHIEN_HUB_AND_SPOKE_CONG_A5/GOI_D_QS_DU_TOAN_THANH_TOAN/03_QS_Dien_Giai_Chi_Tiet_Takeoff_Cong_A5.xlsx
@@ -1145,7 +1145,7 @@
     <row r="23" ht="62" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Quy ước: ván khuôn tính theo diện tích bề mặt bê tông tiếp xúc ván khuôn; mặt nào có ván khuôn do biện pháp thi công quyết định (công tắc 1/0 bên dưới). Căn cứ đo bóc: Thông tư 13/2021/TT-BXD (cần đối chiếu điều khoản cụ thể và bản sửa đổi hiện hành); Thông tư 12/2021/TT-BXD là định mức, không phải đo bóc.</t>
+          <t>Quy ước: ván khuôn tính theo diện tích bề mặt bê tông tiếp xúc ván khuôn; mặt nào có ván khuôn do biện pháp thi công quyết định (công tắc 1/0 bên dưới). Căn cứ đo bóc: văn bản hiện hành tại thời điểm lập hồ sơ do kỹ sư QS xác nhận (theo nguồn thứ cấp: TT 13/2021/TT-BXD và sửa đổi áp dụng đến 30/06/2026; từ 01/07/2026 cần kiểm tra văn bản thay thế như TT 37/2026/TT-BXD, QĐ 1041/QĐ-BXD - chưa đối chiếu toàn văn). TT 12/2021/TT-BXD là định mức, không phải đo bóc.</t>
         </is>
       </c>
     </row>

--- a/examples/HO_SO_CONG_HOP_TUYEN_A5/HO_SO_THUC_CHIEN_HUB_AND_SPOKE_CONG_A5/GOI_D_QS_DU_TOAN_THANH_TOAN/03_QS_Dien_Giai_Chi_Tiet_Takeoff_Cong_A5.xlsx
+++ b/examples/HO_SO_CONG_HOP_TUYEN_A5/HO_SO_THUC_CHIEN_HUB_AND_SPOKE_CONG_A5/GOI_D_QS_DU_TOAN_THANH_TOAN/03_QS_Dien_Giai_Chi_Tiet_Takeoff_Cong_A5.xlsx
@@ -16,8 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,15 @@
       <name val="Times New Roman"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,8 +65,18 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -78,17 +98,45 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,8 +502,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -515,6 +575,56 @@
           <t>GHI CHÚ</t>
         </is>
       </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>RỘNG LÒNG b (m)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>CAO LÒNG h (m)</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>SỐ KHOANG n</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>CẠNH VÚT c (m)</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>VK TRONG (m2/m)</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>VK HÔNG NGOÀI (m2/m)</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>VK ĐẦU ĐỐT (m2/m)</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>VK TÍNH LẠI (m2/m)</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>CHÊNH LỆCH SO VỚI SỐ ĐANG DÙNG (cột F)</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -663,13 +773,25 @@
         <v>1</v>
       </c>
       <c r="I8" s="3">
-        <f>D8*E8*(F8*G8-2.0*2.0+4*0.5*0.2*0.2)</f>
+        <f>D8*E8*(F8*G8-M8*K8*L8+M8*4*0.5*N8^2)</f>
         <v/>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>2.330 m3/m</t>
         </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -702,13 +824,25 @@
         <v>1</v>
       </c>
       <c r="I9" s="3">
-        <f>D9*E9*(F9*G9-3.0*3.0+4*0.5*0.25*0.25)</f>
+        <f>D9*E9*(F9*G9-M9*K9*L9+M9*4*0.5*N9^2)</f>
         <v/>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>4.085 m3/m</t>
         </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="10">
@@ -741,13 +875,25 @@
         <v>1</v>
       </c>
       <c r="I10" s="3">
-        <f>D10*E10*(F10*G10-2*3.0*3.0+8*0.5*0.25*0.25)</f>
+        <f>D10*E10*(F10*G10-M10*K10*L10+M10*4*0.5*N10^2)</f>
         <v/>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>7.090 m3/m</t>
         </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="11">
@@ -785,8 +931,32 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Trong + ngoài + đầu đốt</t>
-        </is>
+          <t>Cột F = VK m2/m ĐANG DÙNG (không phải bề rộng); P..U là tính lại theo hình học</t>
+        </is>
+      </c>
+      <c r="P11" s="7">
+        <f>$C$17*M8*(2*(K8+L8)-4*N8*(2-SQRT(2)))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="7">
+        <f>$C$18*2*G8+$C$19*F8+$C$20*F8</f>
+        <v/>
+      </c>
+      <c r="R11" s="7">
+        <f>$C$21*2*(F8*G8-M8*K8*L8+M8*4*0.5*N8^2)/E8</f>
+        <v/>
+      </c>
+      <c r="S11" s="7">
+        <f>P11+Q11+R11</f>
+        <v/>
+      </c>
+      <c r="T11" s="8">
+        <f>S11/F11-1</f>
+        <v/>
+      </c>
+      <c r="U11" s="7">
+        <f>IF(ABS(T11)&gt;0.05,"LỆCH &gt;5% - QS xác nhận","Khớp (&lt;=5%)")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -824,8 +994,32 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Trong + ngoài + đầu đốt</t>
-        </is>
+          <t>Cột F = VK m2/m ĐANG DÙNG (không phải bề rộng); P..U là tính lại theo hình học</t>
+        </is>
+      </c>
+      <c r="P12" s="7">
+        <f>$C$17*M9*(2*(K9+L9)-4*N9*(2-SQRT(2)))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="7">
+        <f>$C$18*2*G9+$C$19*F9+$C$20*F9</f>
+        <v/>
+      </c>
+      <c r="R12" s="7">
+        <f>$C$21*2*(F9*G9-M9*K9*L9+M9*4*0.5*N9^2)/E9</f>
+        <v/>
+      </c>
+      <c r="S12" s="7">
+        <f>P12+Q12+R12</f>
+        <v/>
+      </c>
+      <c r="T12" s="8">
+        <f>S12/F12-1</f>
+        <v/>
+      </c>
+      <c r="U12" s="7">
+        <f>IF(ABS(T12)&gt;0.05,"LỆCH &gt;5% - QS xác nhận","Khớp (&lt;=5%)")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -863,11 +1057,102 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Trong + ngoài + đầu đốt</t>
+          <t>Cột F = VK m2/m ĐANG DÙNG (không phải bề rộng); P..U là tính lại theo hình học</t>
+        </is>
+      </c>
+      <c r="P13" s="7">
+        <f>$C$17*M10*(2*(K10+L10)-4*N10*(2-SQRT(2)))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="7">
+        <f>$C$18*2*G10+$C$19*F10+$C$20*F10</f>
+        <v/>
+      </c>
+      <c r="R13" s="7">
+        <f>$C$21*2*(F10*G10-M10*K10*L10+M10*4*0.5*N10^2)/E10</f>
+        <v/>
+      </c>
+      <c r="S13" s="7">
+        <f>P13+Q13+R13</f>
+        <v/>
+      </c>
+      <c r="T13" s="8">
+        <f>S13/F13-1</f>
+        <v/>
+      </c>
+      <c r="U13" s="7">
+        <f>IF(ABS(T13)&gt;0.05,"LỆCH &gt;5% - QS xác nhận","Khớp (&lt;=5%)")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>QUY ƯỚC VÁN KHUÔN (1 = có ván khuôn, 0 = không) - đổi ô vàng, cột P..U của dòng 11-13 tự tính lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ván khuôn mặt trong (lòng cống)</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ván khuôn mặt hông ngoài (2 bên)</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ván khuôn mặt trên (bản nắp)</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ván khuôn mặt đáy (bản đáy)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ván khuôn đầu đốt (2 đầu mỗi đốt)</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="62" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Quy ước: ván khuôn tính theo diện tích bề mặt bê tông tiếp xúc ván khuôn; mặt nào có ván khuôn do biện pháp thi công quyết định (công tắc 1/0 bên dưới). Căn cứ đo bóc: văn bản hiện hành tại thời điểm lập hồ sơ do kỹ sư QS xác nhận (theo nguồn thứ cấp: TT 13/2021/TT-BXD và sửa đổi áp dụng đến 30/06/2026; từ 01/07/2026 cần kiểm tra văn bản thay thế như TT 37/2026/TT-BXD, QĐ 1041/QĐ-BXD - chưa đối chiếu toàn văn). TT 12/2021/TT-BXD là định mức, không phải đo bóc.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A23:J23"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>